--- a/quiz_results_flat.xlsx
+++ b/quiz_results_flat.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,101 +413,101 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S38"/>
+  <dimension ref="A1:S39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Candidate Name</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Total Score</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Accuracy (%)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Q1 Question</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Q1 Selected</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Q1 Correct Answer</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Q2 Question</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Q2 Selected</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Q2 Correct Answer</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Q3 Question</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Q3 Selected</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Q3 Correct Answer</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Q4 Question</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Q4 Selected</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Q4 Correct Answer</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Q5 Question</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Q5 Selected</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Q5 Correct Answer</t>
         </is>
@@ -4037,6 +4025,101 @@
       <c r="S38" t="inlineStr">
         <is>
           <t>H2O</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>runo</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2026-07-04 20:38:52</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>3/5</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>60</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>HTML is used for?</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Web page structure</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Web page structure</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2 + 2 × 3 = ?</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>What is the capital of India?</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>New Delhi</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Which of the following is an output device?</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>Keyboard</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Monitor</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>National animal of India?</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>Peacock</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Tiger</t>
         </is>
       </c>
     </row>
